--- a/raw/20250515_r4_GR_reindeer_swabs_67-88.xlsx
+++ b/raw/20250515_r4_GR_reindeer_swabs_67-88.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MNPRO\Desktop\RT-QuIC Data\Gage's RT-QuIC Data\2025\20250515_r4_GR_reindeer_swabs_67-88\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\canadian-reindeer-sentinels\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2BE51CD-2531-46BF-AF5C-50DB16314209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2EC182-9785-41DA-A9D5-D8911A21E7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{751A1984-8BEE-4FB5-A9D3-F4CD32DFFCB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{751A1984-8BEE-4FB5-A9D3-F4CD32DFFCB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="152">
   <si>
     <t>User: USER</t>
   </si>
@@ -481,6 +481,18 @@
   </si>
   <si>
     <t>3. Dilutions</t>
+  </si>
+  <si>
+    <t>Pre-inoc Pen 1</t>
+  </si>
+  <si>
+    <t>Pre-inoc Pen 2</t>
+  </si>
+  <si>
+    <t>Pre-inoc Pen 3</t>
+  </si>
+  <si>
+    <t>Pre-inoc Pen 4</t>
   </si>
 </sst>
 </file>
@@ -1758,17 +1770,17 @@
       <c r="I31" s="14">
         <v>84</v>
       </c>
-      <c r="J31" s="14">
-        <v>85</v>
-      </c>
-      <c r="K31" s="14">
-        <v>86</v>
-      </c>
-      <c r="L31" s="14">
-        <v>87</v>
-      </c>
-      <c r="M31" s="15">
-        <v>88</v>
+      <c r="J31" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -1799,17 +1811,17 @@
       <c r="I32" s="14">
         <v>84</v>
       </c>
-      <c r="J32" s="14">
-        <v>85</v>
-      </c>
-      <c r="K32" s="14">
-        <v>86</v>
-      </c>
-      <c r="L32" s="14">
-        <v>87</v>
-      </c>
-      <c r="M32" s="15">
-        <v>88</v>
+      <c r="J32" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -1840,17 +1852,17 @@
       <c r="I33" s="14">
         <v>84</v>
       </c>
-      <c r="J33" s="14">
-        <v>85</v>
-      </c>
-      <c r="K33" s="14">
-        <v>86</v>
-      </c>
-      <c r="L33" s="14">
-        <v>87</v>
-      </c>
-      <c r="M33" s="15">
-        <v>88</v>
+      <c r="J33" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -1881,17 +1893,17 @@
       <c r="I34" s="17">
         <v>84</v>
       </c>
-      <c r="J34" s="17">
-        <v>85</v>
-      </c>
-      <c r="K34" s="17">
-        <v>86</v>
-      </c>
-      <c r="L34" s="17">
-        <v>87</v>
-      </c>
-      <c r="M34" s="18">
-        <v>88</v>
+      <c r="J34" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="L34" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
